--- a/data/CROSS_REFERENCE_REPORT.xlsx
+++ b/data/CROSS_REFERENCE_REPORT.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,30 +436,40 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>wp_hausgeld</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>wp_ruecklage</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>wp_total</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>actual_payment</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>delta_monthly</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>delta_annual</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>match_confidence</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -476,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,30 +507,40 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>wp_hausgeld</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>wp_ruecklage</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>wp_total</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>actual_payment</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>delta_monthly</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>delta_annual</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>match_confidence</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -543,23 +563,29 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>289</v>
+      </c>
+      <c r="E2" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2" t="n">
         <v>387</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>395</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>96</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -582,23 +608,29 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>330</v>
+      </c>
+      <c r="E3" t="n">
+        <v>110</v>
+      </c>
+      <c r="F3" t="n">
         <v>440</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>445</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>60</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -621,23 +653,29 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>295</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
         <v>395</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>390</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>-5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>-60</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -660,23 +698,29 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>228</v>
+      </c>
+      <c r="E5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F5" t="n">
         <v>310</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>315</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>60</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>fuzzy</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -693,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,30 +758,40 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>wp_hausgeld</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>wp_ruecklage</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>wp_total</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>actual_payment</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>delta_monthly</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>delta_annual</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>match_confidence</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -760,23 +814,29 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>312</v>
+      </c>
+      <c r="E2" t="n">
+        <v>104</v>
+      </c>
+      <c r="F2" t="n">
         <v>416</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>420</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>4</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>48</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -799,23 +859,29 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>308</v>
+      </c>
+      <c r="E3" t="n">
+        <v>105</v>
+      </c>
+      <c r="F3" t="n">
         <v>413</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>410</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>-3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>-36</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -838,23 +904,29 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>301</v>
+      </c>
+      <c r="E4" t="n">
+        <v>102</v>
+      </c>
+      <c r="F4" t="n">
         <v>403</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>400</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>-3</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>-36</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -877,23 +949,29 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>89</v>
+      </c>
+      <c r="F5" t="n">
         <v>334.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>334.5</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -916,23 +994,29 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>198</v>
+      </c>
+      <c r="E6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F6" t="n">
         <v>270</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>270</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>fuzzy</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -955,23 +1039,29 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>220</v>
+      </c>
+      <c r="E7" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" t="n">
         <v>300</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>300</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>fuzzy</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -994,23 +1084,29 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>260</v>
+      </c>
+      <c r="E8" t="n">
+        <v>90</v>
+      </c>
+      <c r="F8" t="n">
         <v>350</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>350</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>fuzzy</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -1033,23 +1129,29 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>215</v>
+      </c>
+      <c r="E9" t="n">
+        <v>78</v>
+      </c>
+      <c r="F9" t="n">
         <v>293</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>293</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -1072,23 +1174,29 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>185</v>
+      </c>
+      <c r="E10" t="n">
+        <v>68</v>
+      </c>
+      <c r="F10" t="n">
         <v>253</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>253</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>fuzzy</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>

--- a/data/CROSS_REFERENCE_REPORT.xlsx
+++ b/data/CROSS_REFERENCE_REPORT.xlsx
@@ -7,9 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Action Required" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correct" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correct" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,121 +424,65 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>street</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>wp_hausgeld</t>
+          <t>unit_number</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>wp_ruecklage</t>
+          <t>hg_2024</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>wp_total</t>
+          <t>hg_2025</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>actual_payment</t>
+          <t>hg_2026</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>delta_monthly</t>
+          <t>latest_hg</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>delta_annual</t>
+          <t>latest_hg_year</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>match_confidence</t>
+          <t>hg_wp_extracted</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>canonical_key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>wp_hausgeld</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>wp_ruecklage</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>wp_total</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>actual_payment</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>delta_monthly</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>delta_annual</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>match_confidence</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+          <t>delta_vs_2026</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>delta_vs_latest</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>needs_wp_update</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
@@ -549,429 +491,218 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BORNHOLMERSTR_80_WE12</t>
+          <t>RESIDENZSTR_129_WE15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bornholmerstr. 80</t>
+          <t>Alfred Rosenfeld</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WE 12</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>289</v>
+          <t>Residenzstr. 129</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>320</v>
       </c>
       <c r="F2" t="n">
-        <v>387</v>
+        <v>334.5</v>
       </c>
       <c r="G2" t="n">
-        <v>395</v>
+        <v>334.5</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>96</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Review</t>
+        <v>334.5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BORNHOLMERSTR_80_WE31</t>
+          <t>RESIDENZSTR_129_WE6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bornholmerstr. 80</t>
+          <t>Hans Müller</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WE 31</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>330</v>
+          <t>Residenzstr. 129</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="F3" t="n">
-        <v>440</v>
-      </c>
-      <c r="G3" t="n">
-        <v>445</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Review</t>
+        <v>270</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>270</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BORNHOLMERSTR_80_WE17</t>
+          <t>RESIDENZSTR_129_WE7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bornholmerstr. 80</t>
+          <t>Bauer Maria</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>WE 17</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+          <t>Residenzstr. 129</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>295</v>
       </c>
-      <c r="E4" t="n">
-        <v>100</v>
-      </c>
       <c r="F4" t="n">
-        <v>395</v>
+        <v>300</v>
       </c>
       <c r="G4" t="n">
-        <v>390</v>
+        <v>300</v>
       </c>
       <c r="H4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-60</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Review</t>
+        <v>300</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>300</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RESIDENZSTR_129_WE8</t>
+          <t>RESIDENZSTR_129_WE9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Schneider Anna</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>Residenzstr. 129</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>WE08</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>228</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="F5" t="n">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="G5" t="n">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>60</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>canonical_key</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>street</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>wp_hausgeld</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>wp_ruecklage</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>wp_total</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>actual_payment</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>delta_monthly</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>delta_annual</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>match_confidence</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BORNHOLMERSTR_80_WE28</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bornholmerstr. 80</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>WE 28</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>312</v>
-      </c>
-      <c r="E2" t="n">
-        <v>104</v>
-      </c>
-      <c r="F2" t="n">
-        <v>416</v>
-      </c>
-      <c r="G2" t="n">
-        <v>420</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BORNHOLMERSTR_80_WE19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bornholmerstr. 80</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>WE 19</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>308</v>
-      </c>
-      <c r="E3" t="n">
-        <v>105</v>
-      </c>
-      <c r="F3" t="n">
-        <v>413</v>
-      </c>
-      <c r="G3" t="n">
-        <v>410</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-36</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BORNHOLMERSTR_80_WE22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bornholmerstr. 80</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>WE 22</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>301</v>
-      </c>
-      <c r="E4" t="n">
-        <v>102</v>
-      </c>
-      <c r="F4" t="n">
-        <v>403</v>
-      </c>
-      <c r="G4" t="n">
-        <v>400</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-36</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RESIDENZSTR_129_WE15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Residenzstr. 129</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>WE15</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>245.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>89</v>
-      </c>
-      <c r="F5" t="n">
-        <v>334.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>334.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+        <v>320</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>320</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -980,43 +711,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RESIDENZSTR_129_WE6</t>
+          <t>RESIDENZSTR_129_WE11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Richter Sabine</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>Residenzstr. 129</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>WE06</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>198</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>285</v>
       </c>
       <c r="F6" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="G6" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+        <v>293</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>293</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -1025,43 +767,54 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RESIDENZSTR_129_WE7</t>
+          <t>RESIDENZSTR_129_WE2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Wolf Ingrid</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>Residenzstr. 129</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>WE07</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>220</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>245</v>
       </c>
       <c r="F7" t="n">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="G7" t="n">
-        <v>300</v>
+        <v>253</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+        <v>253</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>253</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -1070,43 +823,54 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BORNHOLMERSTR_80_WE4</t>
+          <t>RESIDENZSTR_129_WE8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bornholmerstr. 80</t>
+          <t>Becker Helga</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>WE 04</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>260</v>
+          <t>Residenzstr. 129</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="F8" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="G8" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
+        <v>310</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>310</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -1115,43 +879,54 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RESIDENZSTR_129_WE11</t>
+          <t>BORNHOLMERSTR_80_WE28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Residenzstr. 129</t>
+          <t>Shavit Assaf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>WE11</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>215</v>
+          <t>Bornholmerstr. 80</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="F9" t="n">
-        <v>293</v>
+        <v>416</v>
       </c>
       <c r="G9" t="n">
-        <v>293</v>
+        <v>416</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+        <v>416</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>416</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
@@ -1160,43 +935,756 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RESIDENZSTR_129_WE2</t>
+          <t>BORNHOLMERSTR_80_WE12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Residenzstr. 129</t>
+          <t>Fischer Klaus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>WE02</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+          <t>Bornholmerstr. 80</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>375</v>
+      </c>
+      <c r="F10" t="n">
+        <v>387</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>387</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>387</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BORNHOLMERSTR_80_WE22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wagner Thomas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bornholmerstr. 80</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>390</v>
+      </c>
+      <c r="F11" t="n">
+        <v>403</v>
+      </c>
+      <c r="G11" t="n">
+        <v>403</v>
+      </c>
+      <c r="H11" t="n">
+        <v>403</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>403</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BORNHOLMERSTR_80_WE4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hoffmann Petra</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bornholmerstr. 80</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>340</v>
+      </c>
+      <c r="F12" t="n">
+        <v>350</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>350</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>350</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BORNHOLMERSTR_80_WE17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Klein Werner</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bornholmerstr. 80</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>380</v>
+      </c>
+      <c r="F13" t="n">
+        <v>395</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>395</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>395</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BORNHOLMERSTR_80_WE31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Koch Dieter</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bornholmerstr. 80</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>425</v>
+      </c>
+      <c r="F14" t="n">
+        <v>440</v>
+      </c>
+      <c r="G14" t="n">
+        <v>440</v>
+      </c>
+      <c r="H14" t="n">
+        <v>440</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>440</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BORNHOLMERSTR_80_WE19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Schäfer Georg</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bornholmerstr. 80</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>398</v>
+      </c>
+      <c r="F15" t="n">
+        <v>413</v>
+      </c>
+      <c r="G15" t="n">
+        <v>413</v>
+      </c>
+      <c r="H15" t="n">
+        <v>413</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>413</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WUERZBURGERSTR8_WE29</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Avraham Josef</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wuerzburgerstr.8</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>195</v>
+      </c>
+      <c r="F16" t="n">
+        <v>210</v>
+      </c>
+      <c r="G16" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RESIDENZSTR_128_WE12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Levi Sarah</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Residenz str. 128</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>280</v>
+      </c>
+      <c r="F17" t="n">
+        <v>295</v>
+      </c>
+      <c r="G17" t="n">
+        <v>295</v>
+      </c>
+      <c r="H17" t="n">
+        <v>295</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>295</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SONNENALLE_147_WE3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ben-David Roni</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SONNENALLE 147</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>510</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>510</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>510</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WESERSTR_59_WE19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Montag Tanja</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Weserstr. 59</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>340</v>
+      </c>
+      <c r="F19" t="n">
+        <v>355</v>
+      </c>
+      <c r="G19" t="n">
+        <v>355</v>
+      </c>
+      <c r="H19" t="n">
+        <v>355</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>355</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QUITZOWSTR_130_WE8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Katz Miriam</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quitzowstr. 130</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>185</v>
       </c>
-      <c r="E10" t="n">
-        <v>68</v>
-      </c>
-      <c r="F10" t="n">
-        <v>253</v>
-      </c>
-      <c r="G10" t="n">
-        <v>253</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="F20" t="n">
+        <v>195</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>195</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>195</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QUITZOWSTR_130_WE12</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Shapiro Dan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Quitzowstr. 130</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>195</v>
+      </c>
+      <c r="F21" t="n">
+        <v>205</v>
+      </c>
+      <c r="G21" t="n">
+        <v>205</v>
+      </c>
+      <c r="H21" t="n">
+        <v>205</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>205</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KASTANIENALLEE_25_WE4</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Levy Noa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Kastanienallee 25</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>410</v>
+      </c>
+      <c r="F22" t="n">
+        <v>425</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>425</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>425</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="b">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KASTANIENALLEE_25_WE7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cohen David</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Kastanienallee 25</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>385</v>
+      </c>
+      <c r="F23" t="n">
+        <v>400</v>
+      </c>
+      <c r="G23" t="n">
+        <v>400</v>
+      </c>
+      <c r="H23" t="n">
+        <v>400</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>400</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
